--- a/results/Int All Data -0.2/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.2/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>0.0008527514886827725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000919409931936378</v>
+        <v>0.0009159887892747288</v>
       </c>
       <c r="F3" t="n">
         <v>0.0005699571966596982</v>
@@ -1694,13 +1694,13 @@
         <v>0.01431733733057222</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0185546143922486</v>
+        <v>0.018540929821602</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009352287811013025</v>
+        <v>0.009345445525689729</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0007203547105234265</v>
+        <v>-0.000710091282538482</v>
       </c>
       <c r="K3" t="n">
         <v>0.002627658597312553</v>
@@ -1712,10 +1712,10 @@
         <v>-0.000222187950392947</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006750543559958394</v>
+        <v>0.006777678868532648</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001429756811185053</v>
+        <v>0.00143659909650835</v>
       </c>
       <c r="P3" t="n">
         <v>2.200667778058038e-05</v>
@@ -1724,7 +1724,7 @@
         <v>0.03232368840862183</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004182584137148603</v>
+        <v>0.004172320709163652</v>
       </c>
       <c r="S3" t="n">
         <v>0.02265867950486235</v>
@@ -1736,7 +1736,7 @@
         <v>-0.002817977580889507</v>
       </c>
       <c r="V3" t="n">
-        <v>0.009352287811013025</v>
+        <v>0.009365972381659622</v>
       </c>
       <c r="W3" t="n">
         <v>0.0008154366997738582</v>
@@ -1751,7 +1751,7 @@
         <v>-0.0004624123899782372</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3.098973311537089e-05</v>
+        <v>-2.072630513042416e-05</v>
       </c>
       <c r="AB3" t="n">
         <v>-7.459935042021473e-05</v>
@@ -1760,13 +1760,13 @@
         <v>-3.435560547547467e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.002300922307578424</v>
+        <v>-0.002328291448871616</v>
       </c>
       <c r="AE3" t="n">
         <v>0.001891529675566367</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0009692575398793394</v>
+        <v>0.001000047823834181</v>
       </c>
       <c r="AG3" t="n">
         <v>0.001033963827304761</v>
@@ -1778,10 +1778,10 @@
         <v>-0.000374753983913988</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01895663345401018</v>
+        <v>0.01897716030998008</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02761198183259588</v>
+        <v>0.02754375743430298</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01244815073868296</v>
@@ -1790,7 +1790,7 @@
         <v>0.1443736705229713</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0003183934515233089</v>
+        <v>-0.0002054957436888938</v>
       </c>
       <c r="AO3" t="n">
         <v>0.02518224444914204</v>
@@ -1802,7 +1802,7 @@
         <v>-0.0006808409227326128</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001891529675566367</v>
+        <v>0.001894950818228016</v>
       </c>
       <c r="AS3" t="n">
         <v>0.005490909398400879</v>
@@ -1817,7 +1817,7 @@
         <v>-0.00160124857973802</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.001888648092940166</v>
+        <v>-0.001892069235601816</v>
       </c>
       <c r="AX3" t="n">
         <v>-0.0007748334160933056</v>
@@ -1826,13 +1826,13 @@
         <v>0.04687888961835296</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0003436092531299339</v>
+        <v>0.0003538726811148818</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.01206072978348575</v>
+        <v>0.0120637645324243</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.01677822517170395</v>
+        <v>0.01676454060105735</v>
       </c>
       <c r="BC3" t="n">
         <v>0.0007159093576945586</v>
@@ -1856,7 +1856,7 @@
         <v>0.08045226040277664</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01070534667375633</v>
+        <v>0.01073613695771117</v>
       </c>
       <c r="BK3" t="n">
         <v>0.05276758436535293</v>
@@ -1868,7 +1868,7 @@
         <v>0.003406932034542583</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01206718567508595</v>
+        <v>0.01206055013191</v>
       </c>
       <c r="BO3" t="n">
         <v>0.0100069588368458</v>
@@ -1883,7 +1883,7 @@
         <v>0.01393916264397622</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0002995605993947767</v>
+        <v>0.0002616911590426027</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0004897777840813822</v>
@@ -1892,28 +1892,28 @@
         <v>0.005920338875212903</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001499019665338241</v>
+        <v>-0.001173803337429192</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0002720295857510968</v>
+        <v>0.000275361808343566</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.003720589347912366</v>
+        <v>0.004195710069831319</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0005106433122306575</v>
+        <v>-0.000517485597553956</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0005138848033165577</v>
+        <v>-0.0005102840090791582</v>
       </c>
       <c r="CA3" t="n">
         <v>0.007188514186447006</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.002051712452253037</v>
+        <v>0.002109871877501068</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.005002832286198947</v>
+        <v>0.005043678223086341</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.001478427166111299</v>
@@ -1922,7 +1922,7 @@
         <v>0.0001203005437779314</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.000294066067607891</v>
+        <v>-0.001412420414815608</v>
       </c>
       <c r="CG3" t="n">
         <v>0.3981501843339808</v>
@@ -1934,7 +1934,7 @@
         <v>0.2388532131094749</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.000278575175952821</v>
+        <v>0.0002752429533603517</v>
       </c>
       <c r="CK3" t="n">
         <v>0.003324907042677397</v>
@@ -1949,7 +1949,7 @@
         <v>0.0008245678959292214</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.03127627078387489</v>
+        <v>0.03128653421185983</v>
       </c>
       <c r="CP3" t="n">
         <v>-0.0005606933787157973</v>
@@ -1958,13 +1958,13 @@
         <v>0.05289615465705853</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.05929469980514855</v>
+        <v>0.05937680722902813</v>
       </c>
       <c r="CS3" t="n">
         <v>0.305144051049953</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.083239827174678</v>
+        <v>0.08317161106359236</v>
       </c>
       <c r="CU3" t="n">
         <v>0.05761367808236399</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.05922785121791494</v>
+        <v>0.05923437602289812</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.07126777339895973</v>
+        <v>0.07119935054572675</v>
       </c>
       <c r="CZ3" t="n">
         <v>-0.0007039003451505632</v>
@@ -1988,7 +1988,7 @@
         <v>0.0005487977617645899</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.004055943161117525</v>
+        <v>0.004066206589102472</v>
       </c>
       <c r="DC3" t="n">
         <v>0.2540987833652795</v>
@@ -2000,7 +2000,7 @@
         <v>0.1065836648081142</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.305144051049953</v>
+        <v>0.3051474721926146</v>
       </c>
       <c r="DG3" t="n">
         <v>0.001651589193954904</v>
@@ -2015,7 +2015,7 @@
         <v>-0.0008290420051921342</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0001549595029702766</v>
+        <v>0.0002026170437588571</v>
       </c>
       <c r="DL3" t="n">
         <v>-0.0002182327669902529</v>
@@ -2027,25 +2027,25 @@
         <v>0.00392833430544653</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.002950760227842564</v>
+        <v>-0.002947339085180914</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.005002440202602925</v>
+        <v>0.004999019059941276</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.0001003199335414661</v>
+        <v>-9.347764821816872e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.0001003199335414661</v>
+        <v>-0.0001037410762031154</v>
       </c>
       <c r="DS3" t="n">
         <v>-0.0002139141384949993</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0276944271968576</v>
+        <v>0.0276739003408877</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.008027694016881488</v>
+        <v>0.008099538012776113</v>
       </c>
       <c r="DV3" t="n">
         <v>-0.0007690806358862423</v>
@@ -2054,7 +2054,7 @@
         <v>0.00188332265120444</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.001572337150454126</v>
+        <v>0.001575758293115775</v>
       </c>
       <c r="DY3" t="n">
         <v>0.008487841674627671</v>
@@ -2066,7 +2066,7 @@
         <v>0.03068401775960517</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.002950760227842564</v>
+        <v>-0.002950760227842562</v>
       </c>
       <c r="EC3" t="n">
         <v>0.005052969116768973</v>
@@ -2090,7 +2090,7 @@
         <v>0.006474339413430352</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.001042636774080955</v>
+        <v>-0.001076848200697444</v>
       </c>
       <c r="EK3" t="n">
         <v>0.005695663985457044</v>
@@ -2111,7 +2111,7 @@
         <v>0.001596851282600381</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01206942203398139</v>
+        <v>0.0120726364344957</v>
       </c>
       <c r="ER3" t="n">
         <v>-0.00129645364884047</v>
@@ -2120,7 +2120,7 @@
         <v>-0.000275323049577818</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.001110578379964161</v>
+        <v>-0.001080006163719016</v>
       </c>
       <c r="EU3" t="n">
         <v>0.04701695323502727</v>
@@ -2154,7 +2154,7 @@
         <v>0.004117660717434345</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004207089780703857</v>
+        <v>0.004209757337931505</v>
       </c>
       <c r="F4" t="n">
         <v>0.001807352252432321</v>
@@ -2163,13 +2163,13 @@
         <v>0.02869464923974616</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02276497596055387</v>
+        <v>0.02277080550975372</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01848837512871471</v>
+        <v>0.01849304886193249</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005161743615256099</v>
+        <v>0.005166911363332051</v>
       </c>
       <c r="K4" t="n">
         <v>0.01038842484241272</v>
@@ -2181,10 +2181,10 @@
         <v>0.00203785180545423</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01395002447144363</v>
+        <v>0.01394343979908499</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008034037152026304</v>
+        <v>0.008030057670730067</v>
       </c>
       <c r="P4" t="n">
         <v>0.01148096981661444</v>
@@ -2193,7 +2193,7 @@
         <v>0.04546282999559816</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01026145278756088</v>
+        <v>0.01026394686097413</v>
       </c>
       <c r="S4" t="n">
         <v>0.02535689135206143</v>
@@ -2205,7 +2205,7 @@
         <v>0.005613776880009236</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01848837512871471</v>
+        <v>0.01847910012129084</v>
       </c>
       <c r="W4" t="n">
         <v>0.00833088199827142</v>
@@ -2220,7 +2220,7 @@
         <v>0.002701156006901161</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004326891465981674</v>
+        <v>0.004324840218018815</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0007596870705562198</v>
@@ -2229,13 +2229,13 @@
         <v>0.003872188046823849</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.003152491148936604</v>
+        <v>0.003136724457329994</v>
       </c>
       <c r="AE4" t="n">
         <v>0.002829438179455456</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.006397169180964401</v>
+        <v>0.006392908213228711</v>
       </c>
       <c r="AG4" t="n">
         <v>0.002170223922758685</v>
@@ -2247,10 +2247,10 @@
         <v>0.003087855900622136</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0101946141106263</v>
+        <v>0.01019244000016169</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02785494952992771</v>
+        <v>0.02788638860041481</v>
       </c>
       <c r="AL4" t="n">
         <v>0.02140221598069691</v>
@@ -2259,7 +2259,7 @@
         <v>0.05969371123086385</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001097130182340542</v>
+        <v>0.00124777637906311</v>
       </c>
       <c r="AO4" t="n">
         <v>0.05304700471715304</v>
@@ -2271,7 +2271,7 @@
         <v>0.005547237204407212</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.002829438179455456</v>
+        <v>0.002827514499204288</v>
       </c>
       <c r="AS4" t="n">
         <v>0.01865123172437632</v>
@@ -2286,7 +2286,7 @@
         <v>0.003415562782156112</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.004024521454767093</v>
+        <v>0.0040232042917045</v>
       </c>
       <c r="AX4" t="n">
         <v>0.004038272087261651</v>
@@ -2295,13 +2295,13 @@
         <v>0.05199053529606306</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001370796482057225</v>
+        <v>0.00137202154541812</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01290177156224908</v>
+        <v>0.01289935531832681</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01784114848568388</v>
+        <v>0.01785071592257217</v>
       </c>
       <c r="BC4" t="n">
         <v>0.005157666560174785</v>
@@ -2325,7 +2325,7 @@
         <v>0.06664372712108411</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.01701176033239041</v>
+        <v>0.01700041355706068</v>
       </c>
       <c r="BK4" t="n">
         <v>0.06971304552992119</v>
@@ -2337,7 +2337,7 @@
         <v>0.01140661849228355</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01289694382467857</v>
+        <v>0.01289725255763224</v>
       </c>
       <c r="BO4" t="n">
         <v>0.02040841223114647</v>
@@ -2352,7 +2352,7 @@
         <v>0.02856376773256213</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.005685744680149311</v>
+        <v>0.00565243246289304</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002488737864986354</v>
@@ -2361,28 +2361,28 @@
         <v>0.01903135873613816</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.009950214769909569</v>
+        <v>0.0106107300117023</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0005218652994174021</v>
+        <v>0.0005159896620930244</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01215076321996618</v>
+        <v>0.011461017175045</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004462383625989137</v>
+        <v>0.004466402017171047</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004471340459013573</v>
+        <v>0.004476412523298619</v>
       </c>
       <c r="CA4" t="n">
         <v>0.01535721811311565</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01218735531638857</v>
+        <v>0.01217441065145737</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.02102683738804232</v>
+        <v>0.02103892158189557</v>
       </c>
       <c r="CD4" t="n">
         <v>0.009223462612062087</v>
@@ -2391,7 +2391,7 @@
         <v>0.001679267243699008</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002257454644546352</v>
+        <v>0.002070334088295723</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1179799867335566</v>
@@ -2403,7 +2403,7 @@
         <v>0.09447158918873193</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0005161854576816349</v>
+        <v>0.0005220816802594921</v>
       </c>
       <c r="CK4" t="n">
         <v>0.005344817728104462</v>
@@ -2418,7 +2418,7 @@
         <v>0.006698854553185895</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.02578052178215989</v>
+        <v>0.02577931328995605</v>
       </c>
       <c r="CP4" t="n">
         <v>0.0009137233237185337</v>
@@ -2427,13 +2427,13 @@
         <v>0.04453133804085782</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.03804227890769104</v>
+        <v>0.03801302863898041</v>
       </c>
       <c r="CS4" t="n">
         <v>0.1352152854780635</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.06338155377218761</v>
+        <v>0.06338596516773642</v>
       </c>
       <c r="CU4" t="n">
         <v>0.04642539955667551</v>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.07548947132256978</v>
+        <v>0.07548351224377094</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.06261649165299175</v>
+        <v>0.06270893411398515</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.001449762841088044</v>
@@ -2457,7 +2457,7 @@
         <v>0.002231504146528412</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01037651678752613</v>
+        <v>0.01037414009938853</v>
       </c>
       <c r="DC4" t="n">
         <v>0.1280634175563063</v>
@@ -2469,7 +2469,7 @@
         <v>0.05153551288810985</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1352152854780635</v>
+        <v>0.1352149922219454</v>
       </c>
       <c r="DG4" t="n">
         <v>0.005879820619802171</v>
@@ -2484,7 +2484,7 @@
         <v>0.01340177125191384</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0130090799535825</v>
+        <v>0.0131010270917395</v>
       </c>
       <c r="DL4" t="n">
         <v>0.00205463995617169</v>
@@ -2496,25 +2496,25 @@
         <v>0.01123318660964411</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.008082533920129814</v>
+        <v>0.00807802268440601</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0206015657676498</v>
+        <v>0.02060552754590822</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001043269546714516</v>
+        <v>0.001040981484800461</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001043269546714516</v>
+        <v>0.001044579782169616</v>
       </c>
       <c r="DS4" t="n">
         <v>0.004001763064323357</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.04085731550134075</v>
+        <v>0.04082480223757173</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.01419520229436731</v>
+        <v>0.01436879067518479</v>
       </c>
       <c r="DV4" t="n">
         <v>0.001441916998735433</v>
@@ -2523,7 +2523,7 @@
         <v>0.004292549659211406</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01110990400807238</v>
+        <v>0.0111000845060289</v>
       </c>
       <c r="DY4" t="n">
         <v>0.03364347245688808</v>
@@ -2535,7 +2535,7 @@
         <v>0.03324486031352113</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.008082533920129814</v>
+        <v>0.008082533920129812</v>
       </c>
       <c r="EC4" t="n">
         <v>0.007663355531334926</v>
@@ -2559,7 +2559,7 @@
         <v>0.01704661895016961</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.009374378084379688</v>
+        <v>0.009303501984705873</v>
       </c>
       <c r="EK4" t="n">
         <v>0.02054758985189658</v>
@@ -2580,7 +2580,7 @@
         <v>0.005866854749159945</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.02560676810574258</v>
+        <v>0.02560909024280676</v>
       </c>
       <c r="ER4" t="n">
         <v>0.005290913601573406</v>
@@ -2589,7 +2589,7 @@
         <v>0.001163179871611725</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.009314434891244174</v>
+        <v>0.009370092786842041</v>
       </c>
       <c r="EU4" t="n">
         <v>0.04737114183927702</v>
@@ -2650,7 +2650,7 @@
         <v>-0.003786468032278068</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02687196110210698</v>
+        <v>-0.02690437601296597</v>
       </c>
       <c r="O5" t="n">
         <v>-0.01423014586709886</v>
@@ -2767,7 +2767,7 @@
         <v>-0.002017937219730947</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01277147487844409</v>
+        <v>-0.0127390599675851</v>
       </c>
       <c r="BB5" t="n">
         <v>-0.01115072933549434</v>
@@ -2821,7 +2821,7 @@
         <v>-0.0263817480719795</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.006774716369529987</v>
+        <v>-0.006807131280388979</v>
       </c>
       <c r="BT5" t="n">
         <v>-0.00589951377633714</v>
@@ -2830,19 +2830,19 @@
         <v>-0.01274823830877645</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.02175449871465301</v>
+        <v>-0.02178663239074555</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0005664778407197702</v>
+        <v>-0.0005331556147950778</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.01392405063291137</v>
+        <v>-0.009237085186452254</v>
       </c>
       <c r="BY5" t="n">
         <v>-0.01160453808752024</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.01163695299837925</v>
+        <v>-0.01166936790923824</v>
       </c>
       <c r="CA5" t="n">
         <v>-0.01172325432415113</v>
@@ -2860,7 +2860,7 @@
         <v>-0.003310832529733188</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003663239074550184</v>
+        <v>-0.006089633937735183</v>
       </c>
       <c r="CG5" t="n">
         <v>0.260453808752026</v>
@@ -2872,7 +2872,7 @@
         <v>0.06154562383612666</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0005331556147950778</v>
+        <v>-0.0005664778407197702</v>
       </c>
       <c r="CK5" t="n">
         <v>-0.002578150177247785</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.01334245638043105</v>
+        <v>-0.01330824495381457</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.004618542593226105</v>
+        <v>-0.005302771125555927</v>
       </c>
       <c r="CZ5" t="n">
         <v>-0.003061553335481759</v>
@@ -2968,7 +2968,7 @@
         <v>-0.02003241491085902</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01645569620253164</v>
+        <v>-0.01648990762914813</v>
       </c>
       <c r="DQ5" t="n">
         <v>-0.001953875720691889</v>
@@ -2992,7 +2992,7 @@
         <v>-0.005679702048417112</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02712966130687647</v>
+        <v>-0.02709544988025998</v>
       </c>
       <c r="DY5" t="n">
         <v>-0.01384233395406578</v>
@@ -3122,7 +3122,7 @@
         <v>0.001670298585305194</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002870357381884861</v>
+        <v>-0.00285325166857662</v>
       </c>
       <c r="P6" t="n">
         <v>-0.004928201510467988</v>
@@ -3185,10 +3185,10 @@
         <v>-3.854724744321026e-05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01101411237275041</v>
+        <v>0.01106542951267515</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01452248159757298</v>
+        <v>0.01449831143966128</v>
       </c>
       <c r="AL6" t="n">
         <v>-0.005466972035993506</v>
@@ -3236,7 +3236,7 @@
         <v>-4.274813111494746e-05</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.004878952696401769</v>
+        <v>0.004853294126439392</v>
       </c>
       <c r="BB6" t="n">
         <v>0.006727420669727688</v>
@@ -3275,7 +3275,7 @@
         <v>-0.001620078475857103</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.004878952696401769</v>
+        <v>0.0048532941264394</v>
       </c>
       <c r="BO6" t="n">
         <v>0.002180612668367324</v>
@@ -3290,7 +3290,7 @@
         <v>-0.0008898219064710805</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.003266713228069845</v>
+        <v>-0.003242543070158144</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.00124781085362406</v>
@@ -3305,7 +3305,7 @@
         <v>-1.611099059971588e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001697227046430533</v>
+        <v>-0.001673356900026968</v>
       </c>
       <c r="BY6" t="n">
         <v>-0.002132830531140345</v>
@@ -3329,7 +3329,7 @@
         <v>-0.0005438091350637663</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.00162556053811656</v>
+        <v>-0.00172397424219688</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3211719283102611</v>
@@ -3395,7 +3395,7 @@
         <v>-0.0001840738831643179</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.001488270554675872</v>
+        <v>0.001513929124638239</v>
       </c>
       <c r="DC6" t="n">
         <v>0.2012605306604984</v>
@@ -3407,7 +3407,7 @@
         <v>0.06534047235314866</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.297790273840923</v>
+        <v>0.2978159324108853</v>
       </c>
       <c r="DG6" t="n">
         <v>-0.00136090311040285</v>
@@ -3440,10 +3440,10 @@
         <v>-0.003523382447149279</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.000639694503575941</v>
+        <v>-0.0006225887902676974</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.000639694503575941</v>
+        <v>-0.0006482473602300642</v>
       </c>
       <c r="DS6" t="n">
         <v>0.0001040999359384897</v>
@@ -3527,7 +3527,7 @@
         <v>-0.001132124751477315</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.004848709409483629</v>
+        <v>-0.004840701722103743</v>
       </c>
       <c r="EU6" t="n">
         <v>0.01553638536697024</v>
@@ -3570,7 +3570,7 @@
         <v>0.005388393217513655</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00945937982392267</v>
+        <v>0.009390956970689691</v>
       </c>
       <c r="I7" t="n">
         <v>0.008107253806706776</v>
@@ -3600,7 +3600,7 @@
         <v>0.01589033355323412</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001937038482704601</v>
+        <v>0.001885721342779845</v>
       </c>
       <c r="S7" t="n">
         <v>0.02347037427840092</v>
@@ -3627,7 +3627,7 @@
         <v>-0.0002377335726900575</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0005726637801762912</v>
+        <v>-0.0005213466402515576</v>
       </c>
       <c r="AB7" t="n">
         <v>-0.0002314727567246489</v>
@@ -3642,7 +3642,7 @@
         <v>0.0003830426534699005</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0009438167722779224</v>
+        <v>-0.0007898653525037157</v>
       </c>
       <c r="AG7" t="n">
         <v>0.0005319648191274839</v>
@@ -3657,7 +3657,7 @@
         <v>0.02000075069520315</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01677455445060336</v>
+        <v>0.01644954589774669</v>
       </c>
       <c r="AL7" t="n">
         <v>0.005108574562549378</v>
@@ -3678,7 +3678,7 @@
         <v>6.375566756692264e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0003830426534699005</v>
+        <v>0.0004001483667781469</v>
       </c>
       <c r="AS7" t="n">
         <v>-0.004421069178671222</v>
@@ -3693,7 +3693,7 @@
         <v>-0.003045734581796877</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.001543018161361964</v>
+        <v>-0.001560123874670211</v>
       </c>
       <c r="AX7" t="n">
         <v>-0.0002955694120477803</v>
@@ -3732,7 +3732,7 @@
         <v>0.06945090885304997</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005846214646865256</v>
+        <v>0.006000166066639463</v>
       </c>
       <c r="BK7" t="n">
         <v>0.03429652233506468</v>
@@ -3759,7 +3759,7 @@
         <v>0.007862560151953395</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.000428668769602969</v>
+        <v>0.0004446841443627392</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.0001591343093571007</v>
@@ -3786,7 +3786,7 @@
         <v>0.006599881234707577</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0003250085528566482</v>
+        <v>-3.421142661649279e-05</v>
       </c>
       <c r="CC7" t="n">
         <v>0.004662016355427984</v>
@@ -3798,7 +3798,7 @@
         <v>-0.0003392283621590497</v>
       </c>
       <c r="CF7" t="n">
-        <v>-1.607200257152108e-05</v>
+        <v>-0.0007370914002888474</v>
       </c>
       <c r="CG7" t="n">
         <v>0.3795745190636031</v>
@@ -3825,7 +3825,7 @@
         <v>5.213777057939679e-05</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.03100677126803025</v>
+        <v>0.03105808840795498</v>
       </c>
       <c r="CP7" t="n">
         <v>-0.0005510939167025664</v>
@@ -3834,13 +3834,13 @@
         <v>0.03302103512767486</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.04647659015740985</v>
+        <v>0.04688712727680773</v>
       </c>
       <c r="CS7" t="n">
         <v>0.3462032531532669</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.07749822427724895</v>
+        <v>0.0771732157243923</v>
       </c>
       <c r="CU7" t="n">
         <v>0.05028217933049572</v>
@@ -3891,7 +3891,7 @@
         <v>-0.0004715489882616719</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.004425733869176112</v>
+        <v>-0.004409820438240402</v>
       </c>
       <c r="DL7" t="n">
         <v>-6.318062835842242e-05</v>
@@ -4045,7 +4045,7 @@
         <v>0.0161749666438606</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001220474224697729</v>
+        <v>0.001297449934584813</v>
       </c>
       <c r="K8" t="n">
         <v>0.002954413420254434</v>
@@ -4057,7 +4057,7 @@
         <v>0.0004376986365499158</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01526055120809938</v>
+        <v>0.01527662321067089</v>
       </c>
       <c r="O8" t="n">
         <v>0.007036687747290224</v>
@@ -4105,7 +4105,7 @@
         <v>0.0006522213392893938</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.0006854454832765838</v>
+        <v>-0.0008907140429755239</v>
       </c>
       <c r="AE8" t="n">
         <v>0.004638750305587519</v>
@@ -4171,10 +4171,10 @@
         <v>0.06785633570901782</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.000922772114224779</v>
+        <v>0.0009484306841871487</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.02146027611520845</v>
+        <v>0.02146831211649421</v>
       </c>
       <c r="BB8" t="n">
         <v>0.02436251400822969</v>
@@ -4213,7 +4213,7 @@
         <v>0.002613343666840615</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.02146831211649421</v>
+        <v>0.02146027611520845</v>
       </c>
       <c r="BO8" t="n">
         <v>0.02981481369592504</v>
@@ -4258,7 +4258,7 @@
         <v>0.004269229920588888</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.01180679946077005</v>
+        <v>0.01190088088396539</v>
       </c>
       <c r="CD8" t="n">
         <v>0.002415020408749666</v>
@@ -4267,7 +4267,7 @@
         <v>0.001325424306068057</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0001751477441288479</v>
+        <v>1.613415662596596e-05</v>
       </c>
       <c r="CG8" t="n">
         <v>0.438332799487508</v>
@@ -4309,7 +4309,7 @@
         <v>0.3788911753755916</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.1187671333125099</v>
+        <v>0.1187590973112242</v>
       </c>
       <c r="CU8" t="n">
         <v>0.09541372066005771</v>
@@ -4456,7 +4456,7 @@
         <v>0.0002568635555943305</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.02546022194807498</v>
+        <v>0.02548432995193227</v>
       </c>
       <c r="ER8" t="n">
         <v>9.640102827760678e-05</v>
@@ -4604,7 +4604,7 @@
         <v>0.2588556734169077</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001478149100257042</v>
+        <v>0.001710571330824506</v>
       </c>
       <c r="AO9" t="n">
         <v>0.1735776277724205</v>
@@ -4706,7 +4706,7 @@
         <v>0.05173521850899739</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01542935340403694</v>
+        <v>0.01871365035921997</v>
       </c>
       <c r="BW9" t="n">
         <v>0.001265822784810144</v>
@@ -4727,7 +4727,7 @@
         <v>0.03189627228525119</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.04787917737789198</v>
+        <v>0.04791131105398453</v>
       </c>
       <c r="CD9" t="n">
         <v>0.01543882126841766</v>
@@ -4736,7 +4736,7 @@
         <v>0.00253856041131102</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.005029079712624007</v>
+        <v>0.0003103662321539802</v>
       </c>
       <c r="CG9" t="n">
         <v>0.5987146529562982</v>
@@ -4829,7 +4829,7 @@
         <v>0.02937619350732016</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.02487170715018816</v>
+        <v>0.02531645569620255</v>
       </c>
       <c r="DL9" t="n">
         <v>0.003084832904884283</v>
@@ -4856,10 +4856,10 @@
         <v>0.0039106145251397</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08600752651385565</v>
+        <v>0.0858022579541567</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.03876154635648309</v>
+        <v>0.03947998631542936</v>
       </c>
       <c r="DV9" t="n">
         <v>0.000307902839548424</v>
@@ -4904,7 +4904,7 @@
         <v>0.04366645448758749</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.01652411905576464</v>
+        <v>0.01618200478959975</v>
       </c>
       <c r="EK9" t="n">
         <v>0.05460143687991793</v>
@@ -4934,7 +4934,7 @@
         <v>0.001117318435754211</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.01621621621621624</v>
+        <v>0.01648990762914815</v>
       </c>
       <c r="EU9" t="n">
         <v>0.1594021215043395</v>
